--- a/output/rose_water_customers.xlsx
+++ b/output/rose_water_customers.xlsx
@@ -468,7 +468,7 @@
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
@@ -591,7 +591,11 @@
           <t>06AOGPR9376E2ZH</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Nuerma Science Rose Water (Gulab Jal) Cleanses, Hydrates &amp; Moisturizes Skin 100ml</t>
+        </is>
+      </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/earth-science-ayurveda-29503048/</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:58:33</t>
+          <t>2026-10-02 08:08:38</t>
         </is>
       </c>
     </row>
@@ -656,7 +660,11 @@
           <t>29AEJPJ3915J1Z8</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Rose Floral Water</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/falcon-1026607/</t>
@@ -679,7 +687,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:58:37</t>
+          <t>2026-10-02 08:08:38</t>
         </is>
       </c>
     </row>
@@ -721,7 +729,11 @@
           <t>24AAFCG0477K1ZJ</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Rose Water (Regular) 1000ml</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/girnar-ayurvedic-pharmacy-pvt-ltd-23619088/</t>
@@ -744,7 +756,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:58:39</t>
+          <t>2026-10-02 08:08:39</t>
         </is>
       </c>
     </row>
@@ -786,7 +798,11 @@
           <t>27ABOPV9256G1ZU</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>100% Natural Premium Rose Water (No Artificial Fragrance)</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/j-p-pharma-1835999/</t>
@@ -809,7 +825,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:58:42</t>
+          <t>2026-10-02 08:08:39</t>
         </is>
       </c>
     </row>
@@ -851,7 +867,11 @@
           <t>09AAYCS8741F1ZK</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Rose Water</t>
+        </is>
+      </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/sivaroma-naturals-pvt-ltd-22503066/</t>
@@ -874,7 +894,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:58:48</t>
+          <t>2026-10-02 08:08:40</t>
         </is>
       </c>
     </row>
@@ -916,7 +936,11 @@
           <t>24ARHPG5465D1Z0</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Rose Water</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/astral-nutritions-24770557/</t>
@@ -939,7 +963,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:06</t>
+          <t>2026-10-02 08:08:40</t>
         </is>
       </c>
     </row>
@@ -981,7 +1005,11 @@
           <t>09BUFPP5091N1ZV</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>100% Herbal Gulab Jal Rose Water</t>
+        </is>
+      </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/varah-healthcare-12584843/</t>
@@ -1004,7 +1032,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:11</t>
+          <t>2026-10-02 08:08:40</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1074,11 @@
           <t>09ABACA5380M1ZC</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Cannarma Bulgarian Rose Water</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/agrosaf-pharmaceuticals-private-limited-28937259/</t>
@@ -1069,7 +1101,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:11</t>
+          <t>2026-10-02 08:08:41</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1143,11 @@
           <t>09ALIPM4871A1Z3</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Rose Water</t>
+        </is>
+      </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/shubham-natural-fragrances-3330049/</t>
@@ -1134,7 +1170,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:15</t>
+          <t>2026-10-02 08:08:41</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1212,11 @@
           <t>09AAHCR0680B1ZK</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Tota Gulab Jal</t>
+        </is>
+      </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/radha-kishan-bishan-dass-rang-rasayan-pvt-ltd-7759930/</t>
@@ -1199,7 +1239,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:17</t>
+          <t>2026-10-02 08:08:41</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1281,11 @@
           <t>06BGIPG9360E1ZF</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Rose Hydrosol Floral Water</t>
+        </is>
+      </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/rv-international-149006628/</t>
@@ -1264,7 +1308,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:21</t>
+          <t>2026-10-02 08:08:41</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1350,11 @@
           <t>08AALCS1813M1Z1</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Rose Water</t>
+        </is>
+      </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/sunrise-agriland-development-research-pvt-ltd-2157511/</t>
@@ -1329,7 +1377,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:23</t>
+          <t>2026-10-02 08:08:42</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1419,11 @@
           <t>07AFTPC2627M1Z4</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Gulab Jal Rose Water</t>
+        </is>
+      </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/akshay-enterprises-4100868/</t>
@@ -1394,7 +1446,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:26</t>
+          <t>2026-10-02 08:08:42</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1488,11 @@
           <t>09ACVPJ4648N1ZM</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Rose Water For Normal To Oily Skin</t>
+        </is>
+      </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/indus-nutricare-27598150/</t>
@@ -1459,7 +1515,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:35</t>
+          <t>2026-10-02 08:08:42</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1557,11 @@
           <t>24DJEPS5728H1ZY</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Rose Water</t>
+        </is>
+      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/spatz-cosmeceuticals-inc-7548980/</t>
@@ -1524,7 +1584,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:35</t>
+          <t>2026-10-02 08:08:43</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1626,11 @@
           <t>10CDJPK6355C1ZX</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Rose Water</t>
+        </is>
+      </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/shree-manokamna-enterprises-34422803/</t>
@@ -1589,7 +1653,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:39</t>
+          <t>2026-10-02 08:08:43</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1695,11 @@
           <t>09AFAPT3842G1ZC</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Rose Water</t>
+        </is>
+      </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/r-k-essential-oils-company-26864664/</t>
@@ -1654,7 +1722,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:42</t>
+          <t>2026-10-02 08:08:43</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1764,11 @@
           <t>24ACKFS2205H1ZD</t>
         </is>
       </c>
-      <c r="J19" s="2" t="n"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Vedawell Premium Rose water</t>
+        </is>
+      </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/satyam-health-care-29685157/</t>
@@ -1719,7 +1791,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:46</t>
+          <t>2026-10-02 08:08:43</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1833,11 @@
           <t>19ACOPC0757E1ZO</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Rose Water</t>
+        </is>
+      </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/floem-industries-153012010/</t>
@@ -1784,7 +1860,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:47</t>
+          <t>2026-10-02 08:08:44</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1902,11 @@
           <t>03AANFN3604J1ZD</t>
         </is>
       </c>
-      <c r="J21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Rose Water Toning Mist</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/naturealms-organic-studio-8422925/</t>
@@ -1849,7 +1929,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:50</t>
+          <t>2026-10-02 08:08:44</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1971,11 @@
           <t>09AWEPM1098G1ZC</t>
         </is>
       </c>
-      <c r="J22" s="2" t="n"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Pure Rose Water</t>
+        </is>
+      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/meena-perfumery-2740858/</t>
@@ -1914,7 +1998,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:54</t>
+          <t>2026-10-02 08:08:44</t>
         </is>
       </c>
     </row>
@@ -1956,7 +2040,11 @@
           <t>09BKWPJ7765A1ZM</t>
         </is>
       </c>
-      <c r="J23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Gulab Jal Rose Water</t>
+        </is>
+      </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/suman-trading-company-153177345/</t>
@@ -1979,7 +2067,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 05:59:57</t>
+          <t>2026-10-02 08:08:45</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2109,11 @@
           <t>24AKVPT8273D1ZJ</t>
         </is>
       </c>
-      <c r="J24" s="2" t="n"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Shreeji Rose Water</t>
+        </is>
+      </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/k-v-associates-152593154/</t>
@@ -2044,7 +2136,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 06:00:02</t>
+          <t>2026-10-02 08:08:45</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2178,11 @@
           <t>07CUNPK7550A1ZM</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Rose water</t>
+        </is>
+      </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/james-wild-herbs-5399184/</t>
@@ -2109,7 +2205,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 06:00:11</t>
+          <t>2026-10-02 08:08:45</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2247,11 @@
           <t>06AJXPN1585D1ZU</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Gulab Jal</t>
+        </is>
+      </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/sukh-darshan-pharmacy-10526655/</t>
@@ -2174,7 +2274,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 06:00:12</t>
+          <t>2026-10-02 08:08:46</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2316,11 @@
           <t>09CXOPM6575M1ZD</t>
         </is>
       </c>
-      <c r="J27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Rose Water</t>
+        </is>
+      </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/aaron-aromatics-60658070/</t>
@@ -2239,7 +2343,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 06:00:15</t>
+          <t>2026-10-02 08:08:46</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2385,11 @@
           <t>06BFDPA6691E1ZO</t>
         </is>
       </c>
-      <c r="J28" s="2" t="n"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Natural And Organic Hans Ayurvedic Beauty Gulab Jal For Personal Uses, 50ml Pack</t>
+        </is>
+      </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/hans-herbal-overseas-29650604/</t>
@@ -2304,7 +2412,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 06:00:18</t>
+          <t>2026-10-02 08:08:46</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2454,11 @@
           <t>08AZDPM9364R1ZD</t>
         </is>
       </c>
-      <c r="J29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Rose Water Grade B</t>
+        </is>
+      </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
           <t>https://www.tradeindia.com/vaibhav-perfumery-7818036/</t>
@@ -2369,7 +2481,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2026-10-02 06:00:21</t>
+          <t>2026-10-02 08:08:46</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2531,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2432,36 +2544,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated at</t>
+          <t>Last Updated</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 06:09:12 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Leads</t>
-        </is>
+          <t>2026-10-02 08:08:47 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Total Leads</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Total leads</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>28</v>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Leads by source</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TradeIndia</t>
+          <t xml:space="preserve">  TradeIndia</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2471,7 +2583,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t xml:space="preserve">  Meesho</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2576,7 +2688,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
@@ -2586,7 +2698,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -2596,7 +2708,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
@@ -2646,7 +2758,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2656,7 +2768,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
